--- a/output_excel/geral_resultados.xlsx
+++ b/output_excel/geral_resultados.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="11">
   <si>
     <t>Mean</t>
   </si>
@@ -24,10 +24,22 @@
     <t>Std</t>
   </si>
   <si>
+    <t>KNN</t>
+  </si>
+  <si>
     <t>LPMD</t>
   </si>
   <si>
+    <t>LPMD2</t>
+  </si>
+  <si>
+    <t>MICE</t>
+  </si>
+  <si>
     <t>PMIVAE</t>
+  </si>
+  <si>
+    <t>SAEI</t>
   </si>
   <si>
     <t>auc</t>
@@ -394,116 +406,220 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:15">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="K2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>0.6753080367356277</v>
+        <v>0.7623926354151518</v>
       </c>
       <c r="C4">
-        <v>0.7180791145101372</v>
+        <v>0.7593581460675645</v>
       </c>
       <c r="D4">
-        <v>0.5898277064200194</v>
+        <v>0.7503818624159917</v>
       </c>
       <c r="E4">
-        <v>0.06160257822219413</v>
+        <v>0.7592455223966263</v>
       </c>
       <c r="F4">
-        <v>0.04853627984245161</v>
+        <v>0.7548149679784952</v>
       </c>
       <c r="G4">
-        <v>0.147181747980591</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>0.753960999422895</v>
+      </c>
+      <c r="H4">
+        <v>0.7538109503204018</v>
+      </c>
+      <c r="I4">
+        <v>0.04996514325169027</v>
+      </c>
+      <c r="J4">
+        <v>0.03677359668649209</v>
+      </c>
+      <c r="K4">
+        <v>0.04619824844849135</v>
+      </c>
+      <c r="L4">
+        <v>0.04917228509441164</v>
+      </c>
+      <c r="M4">
+        <v>0.03939244096894545</v>
+      </c>
+      <c r="N4">
+        <v>0.0389230521054012</v>
+      </c>
+      <c r="O4">
+        <v>0.03853971340068834</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>0.5428571428571429</v>
+        <v>0.6802960366597816</v>
       </c>
       <c r="C5">
-        <v>0.5714285714285714</v>
+        <v>0.6684552045359305</v>
       </c>
       <c r="D5">
-        <v>0.3761904761904762</v>
+        <v>0.6720833059942208</v>
       </c>
       <c r="E5">
-        <v>0.03912303982179757</v>
+        <v>0.6921959606351773</v>
       </c>
       <c r="F5">
-        <v>0.08748177652797065</v>
+        <v>0.6790259271021153</v>
       </c>
       <c r="G5">
-        <v>0.2064712703683695</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>0.6603446084207966</v>
+      </c>
+      <c r="H5">
+        <v>0.6664210477047831</v>
+      </c>
+      <c r="I5">
+        <v>0.06661650266690183</v>
+      </c>
+      <c r="J5">
+        <v>0.05962165559770144</v>
+      </c>
+      <c r="K5">
+        <v>0.07180470265059333</v>
+      </c>
+      <c r="L5">
+        <v>0.06120032265401377</v>
+      </c>
+      <c r="M5">
+        <v>0.06999525006628859</v>
+      </c>
+      <c r="N5">
+        <v>0.05749908584169461</v>
+      </c>
+      <c r="O5">
+        <v>0.06961559139283455</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>0.6973919011667811</v>
+        <v>0.7056750519000387</v>
       </c>
       <c r="C6">
-        <v>0.6952871196522535</v>
+        <v>0.7052743066831757</v>
       </c>
       <c r="D6">
-        <v>0.5001143902997025</v>
+        <v>0.7184324110878931</v>
       </c>
       <c r="E6">
-        <v>0.05779391455567295</v>
+        <v>0.7015904165413995</v>
       </c>
       <c r="F6">
-        <v>0.03602789635377044</v>
+        <v>0.6878750800889641</v>
       </c>
       <c r="G6">
-        <v>0.05028257202823844</v>
+        <v>0.6949142634659516</v>
+      </c>
+      <c r="H6">
+        <v>0.6983733252878668</v>
+      </c>
+      <c r="I6">
+        <v>0.06272657636502829</v>
+      </c>
+      <c r="J6">
+        <v>0.0624650939531382</v>
+      </c>
+      <c r="K6">
+        <v>0.06509414052250115</v>
+      </c>
+      <c r="L6">
+        <v>0.06688177932382641</v>
+      </c>
+      <c r="M6">
+        <v>0.06129645077283601</v>
+      </c>
+      <c r="N6">
+        <v>0.06262148370506686</v>
+      </c>
+      <c r="O6">
+        <v>0.05703351210171824</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -511,116 +627,220 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:15">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="K2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>0.6724281247616868</v>
+        <v>0.7453467472814307</v>
       </c>
       <c r="C4">
-        <v>0.7065142552102058</v>
+        <v>0.7381120638830805</v>
       </c>
       <c r="D4">
-        <v>0.5027470013400006</v>
+        <v>0.6696765013220892</v>
       </c>
       <c r="E4">
-        <v>0.1298827780764386</v>
+        <v>0.7395367841032416</v>
       </c>
       <c r="F4">
-        <v>0.1554420232386667</v>
+        <v>0.7365913072409629</v>
       </c>
       <c r="G4">
-        <v>0.1668141971911657</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>0.7183174318596126</v>
+      </c>
+      <c r="H4">
+        <v>0.7203850956779563</v>
+      </c>
+      <c r="I4">
+        <v>0.05088774013688706</v>
+      </c>
+      <c r="J4">
+        <v>0.06057949770823182</v>
+      </c>
+      <c r="K4">
+        <v>0.06851078654228991</v>
+      </c>
+      <c r="L4">
+        <v>0.05091770171550947</v>
+      </c>
+      <c r="M4">
+        <v>0.07972912952538697</v>
+      </c>
+      <c r="N4">
+        <v>0.06985352118789732</v>
+      </c>
+      <c r="O4">
+        <v>0.03596244148498645</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>0.6714285714285715</v>
+        <v>0.6873461682812053</v>
       </c>
       <c r="C5">
-        <v>0.7285714285714285</v>
+        <v>0.7077877496279694</v>
       </c>
       <c r="D5">
-        <v>0.4047619047619048</v>
+        <v>0.6630581487615164</v>
       </c>
       <c r="E5">
-        <v>0.149071198499986</v>
+        <v>0.6649233629995511</v>
       </c>
       <c r="F5">
-        <v>0.2113556287730681</v>
+        <v>0.6890170954751801</v>
       </c>
       <c r="G5">
-        <v>0.3794613678692673</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>0.6662449488255554</v>
+      </c>
+      <c r="H5">
+        <v>0.6210968933144715</v>
+      </c>
+      <c r="I5">
+        <v>0.1028102880767158</v>
+      </c>
+      <c r="J5">
+        <v>0.09921213069890991</v>
+      </c>
+      <c r="K5">
+        <v>0.09933985725880598</v>
+      </c>
+      <c r="L5">
+        <v>0.1084824820041741</v>
+      </c>
+      <c r="M5">
+        <v>0.09020752923036744</v>
+      </c>
+      <c r="N5">
+        <v>0.08095680995587023</v>
+      </c>
+      <c r="O5">
+        <v>0.09157852023738766</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>0.5598261267444521</v>
+        <v>0.6791720209876104</v>
       </c>
       <c r="C6">
-        <v>0.5343857240905971</v>
+        <v>0.6730292401510825</v>
       </c>
       <c r="D6">
-        <v>0.5707389613360787</v>
+        <v>0.6053600015342679</v>
       </c>
       <c r="E6">
-        <v>0.1027293676066154</v>
+        <v>0.6851037397800105</v>
       </c>
       <c r="F6">
-        <v>0.08782499544937888</v>
+        <v>0.6526644934121631</v>
       </c>
       <c r="G6">
-        <v>0.06768337834691536</v>
+        <v>0.6606961848218056</v>
+      </c>
+      <c r="H6">
+        <v>0.6823534807133977</v>
+      </c>
+      <c r="I6">
+        <v>0.08087361347500381</v>
+      </c>
+      <c r="J6">
+        <v>0.07133176333630414</v>
+      </c>
+      <c r="K6">
+        <v>0.1258715094426343</v>
+      </c>
+      <c r="L6">
+        <v>0.06597306055740429</v>
+      </c>
+      <c r="M6">
+        <v>0.08428565517543575</v>
+      </c>
+      <c r="N6">
+        <v>0.07710886335501166</v>
+      </c>
+      <c r="O6">
+        <v>0.06481809549115775</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -628,116 +848,220 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:15">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="K2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>0.7051895065965073</v>
+        <v>0.7543751219556807</v>
       </c>
       <c r="C4">
-        <v>0.7348983015764072</v>
+        <v>0.7546597834214694</v>
       </c>
       <c r="D4">
-        <v>0.4123067621008595</v>
+        <v>0.6966149479560577</v>
       </c>
       <c r="E4">
-        <v>0.0431518104006658</v>
+        <v>0.7610860962362943</v>
       </c>
       <c r="F4">
-        <v>0.07606687059164607</v>
+        <v>0.7625303854349486</v>
       </c>
       <c r="G4">
-        <v>0.112356691406537</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>0.7636877796237114</v>
+      </c>
+      <c r="H4">
+        <v>0.7580626438950208</v>
+      </c>
+      <c r="I4">
+        <v>0.03158770498822208</v>
+      </c>
+      <c r="J4">
+        <v>0.03197642326139669</v>
+      </c>
+      <c r="K4">
+        <v>0.0630718587277678</v>
+      </c>
+      <c r="L4">
+        <v>0.0269193632659871</v>
+      </c>
+      <c r="M4">
+        <v>0.03496959663204802</v>
+      </c>
+      <c r="N4">
+        <v>0.03039713421273739</v>
+      </c>
+      <c r="O4">
+        <v>0.03250542625932935</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>0.5809523809523809</v>
+        <v>0.6971116949287477</v>
       </c>
       <c r="C5">
-        <v>0.7</v>
+        <v>0.6678501177987685</v>
       </c>
       <c r="D5">
-        <v>0.3619047619047618</v>
+        <v>0.7016447078914239</v>
       </c>
       <c r="E5">
-        <v>0.1730085916627138</v>
+        <v>0.7087073542650327</v>
       </c>
       <c r="F5">
-        <v>0.138423255749987</v>
+        <v>0.6977900154936219</v>
       </c>
       <c r="G5">
-        <v>0.06388765649999396</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>0.6965770774882311</v>
+      </c>
+      <c r="H5">
+        <v>0.6737821497028565</v>
+      </c>
+      <c r="I5">
+        <v>0.09361015828655841</v>
+      </c>
+      <c r="J5">
+        <v>0.0919166441965128</v>
+      </c>
+      <c r="K5">
+        <v>0.1005319372803368</v>
+      </c>
+      <c r="L5">
+        <v>0.08534172314480391</v>
+      </c>
+      <c r="M5">
+        <v>0.07437930799917401</v>
+      </c>
+      <c r="N5">
+        <v>0.07959337720670008</v>
+      </c>
+      <c r="O5">
+        <v>0.05766654745960811</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>0.6588194921070694</v>
+        <v>0.6959234565800974</v>
       </c>
       <c r="C6">
-        <v>0.6673758865248226</v>
+        <v>0.7054372640707478</v>
       </c>
       <c r="D6">
-        <v>0.4722489132921528</v>
+        <v>0.5839775345292773</v>
       </c>
       <c r="E6">
-        <v>0.0786594313919972</v>
+        <v>0.6932991422968148</v>
       </c>
       <c r="F6">
-        <v>0.07093657830260734</v>
+        <v>0.6909637002549025</v>
       </c>
       <c r="G6">
-        <v>0.09171069193476336</v>
+        <v>0.6844510884862485</v>
+      </c>
+      <c r="H6">
+        <v>0.7128010008076286</v>
+      </c>
+      <c r="I6">
+        <v>0.06786111963380048</v>
+      </c>
+      <c r="J6">
+        <v>0.06408218207441375</v>
+      </c>
+      <c r="K6">
+        <v>0.113467341742424</v>
+      </c>
+      <c r="L6">
+        <v>0.06417000778873028</v>
+      </c>
+      <c r="M6">
+        <v>0.06997165047436141</v>
+      </c>
+      <c r="N6">
+        <v>0.06172832559849065</v>
+      </c>
+      <c r="O6">
+        <v>0.05180041349366615</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
